--- a/reports/seeded_teams.xlsx
+++ b/reports/seeded_teams.xlsx
@@ -8,15 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a11khan\Documents\Here_Projects\OfficePrj\TLOL_Dash\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F0C8B9-7611-49FF-A292-AA9465DC1716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C8ADDA-985F-4139-B26F-C62160F9DC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{D42FFFD5-6F28-4196-B78D-AA8DC1C235B4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{D42FFFD5-6F28-4196-B78D-AA8DC1C235B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Foosball" sheetId="1" r:id="rId1"/>
     <sheet name="Carrom" sheetId="2" r:id="rId2"/>
     <sheet name="Chess" sheetId="3" r:id="rId3"/>
+    <sheet name="Table Tennis" sheetId="4" r:id="rId4"/>
+    <sheet name="Badminton" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Carrom!$A$1:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Chess!$A$1:$C$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foosball!$A$1:$D$25</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="68">
   <si>
     <t>Player 1</t>
   </si>
@@ -223,28 +230,22 @@
     <t xml:space="preserve">Pritam </t>
   </si>
   <si>
-    <t>Points</t>
-  </si>
-  <si>
-    <t>Winner</t>
-  </si>
-  <si>
-    <t>Loser</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
     <t>Player</t>
   </si>
   <si>
-    <t>Round 1</t>
-  </si>
-  <si>
-    <t>Eliminated</t>
-  </si>
-  <si>
     <t>Seed</t>
+  </si>
+  <si>
+    <t>Gully Gang</t>
+  </si>
+  <si>
+    <t>Dabangg Dynamos</t>
+  </si>
+  <si>
+    <t>Rockstar Rebels</t>
+  </si>
+  <si>
+    <t>Badshah Blasters</t>
   </si>
 </sst>
 </file>
@@ -1105,17 +1106,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F23CA2-6A6C-45FB-9B86-B9BAA1F7A58B}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1123,19 +1123,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1146,16 +1140,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1166,16 +1154,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1186,16 +1168,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1206,16 +1182,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1226,16 +1196,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1246,16 +1210,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1266,16 +1224,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1286,16 +1238,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1306,16 +1252,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1326,16 +1266,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1346,16 +1280,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -1366,16 +1294,10 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -1386,16 +1308,10 @@
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" t="s">
         <v>64</v>
       </c>
-      <c r="F14">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1406,16 +1322,10 @@
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" t="s">
         <v>64</v>
       </c>
-      <c r="F15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -1426,16 +1336,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" t="s">
         <v>64</v>
       </c>
-      <c r="F16">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -1446,16 +1350,10 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" t="s">
-        <v>63</v>
-      </c>
-      <c r="F17">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -1466,16 +1364,10 @@
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1486,16 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" t="s">
         <v>64</v>
       </c>
-      <c r="F19">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1506,16 +1392,10 @@
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1526,16 +1406,10 @@
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -1546,16 +1420,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" t="s">
-        <v>63</v>
-      </c>
-      <c r="F22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1566,16 +1434,10 @@
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -1586,16 +1448,10 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E24" t="s">
-        <v>63</v>
-      </c>
-      <c r="F24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1606,13 +1462,7 @@
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" t="s">
-        <v>63</v>
-      </c>
-      <c r="F25">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1622,13 +1472,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6643A701-20FF-4111-A994-F7CC2357235D}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1636,19 +1486,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -1659,16 +1503,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -1679,16 +1517,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
         <v>64</v>
       </c>
-      <c r="F3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -1699,16 +1531,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
         <v>64</v>
       </c>
-      <c r="F4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -1719,16 +1545,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1739,16 +1559,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
         <v>64</v>
       </c>
-      <c r="F6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -1759,16 +1573,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1779,16 +1587,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -1799,16 +1601,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1819,16 +1615,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1839,16 +1629,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1859,16 +1643,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>56</v>
       </c>
@@ -1879,16 +1657,10 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1899,16 +1671,10 @@
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1919,16 +1685,10 @@
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -1939,16 +1699,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1959,16 +1713,10 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>63</v>
-      </c>
-      <c r="F17">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1979,16 +1727,10 @@
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1999,16 +1741,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -2019,16 +1755,10 @@
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -2039,16 +1769,10 @@
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -2059,16 +1783,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" t="s">
-        <v>63</v>
-      </c>
-      <c r="F22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -2079,16 +1797,10 @@
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -2099,16 +1811,10 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E24" t="s">
-        <v>63</v>
-      </c>
-      <c r="F24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2119,13 +1825,7 @@
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" t="s">
-        <v>63</v>
-      </c>
-      <c r="F25">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2135,6 +1835,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FE99394-268D-4AAF-8102-131EFBDB31BD}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2144,16 +1845,16 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -2169,13 +1870,13 @@
         <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -2186,7 +1887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2202,7 +1903,7 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -2213,13 +1914,13 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2235,7 +1936,7 @@
         <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -2246,7 +1947,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -2257,7 +1958,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -2268,7 +1969,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -2279,13 +1980,13 @@
         <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -2301,13 +2002,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2323,13 +2024,13 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -2345,7 +2046,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -2356,7 +2057,7 @@
         <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -2367,13 +2068,13 @@
         <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -2389,7 +2090,7 @@
         <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -2400,7 +2101,7 @@
         <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -2411,13 +2112,13 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -2433,13 +2134,13 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C27">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -2455,13 +2156,13 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -2477,13 +2178,13 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -2499,7 +2200,7 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -2510,7 +2211,7 @@
         <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -2521,7 +2222,7 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C35">
         <v>3</v>
@@ -2532,7 +2233,7 @@
         <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -2543,7 +2244,7 @@
         <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -2554,13 +2255,13 @@
         <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -2576,13 +2277,13 @@
         <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>29</v>
       </c>
@@ -2598,13 +2299,13 @@
         <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>20</v>
       </c>
@@ -2620,7 +2321,7 @@
         <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C44">
         <v>3</v>
@@ -2631,7 +2332,7 @@
         <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C45">
         <v>3</v>
@@ -2642,7 +2343,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -2653,7 +2354,7 @@
         <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C47">
         <v>3</v>
@@ -2664,13 +2365,13 @@
         <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -2679,6 +2380,733 @@
       </c>
       <c r="C49">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C49" xr:uid="{4FE99394-268D-4AAF-8102-131EFBDB31BD}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="3"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD4D867-1FA3-4124-9455-BFE44F482783}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBF24F6F-62A7-4781-BE48-C5BAE16E1D19}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/reports/seeded_teams.xlsx
+++ b/reports/seeded_teams.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foosball" sheetId="1" state="visible" r:id="rId1"/>
@@ -859,6 +859,9 @@
           <t>w</t>
         </is>
       </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -892,6 +895,9 @@
           <t>w</t>
         </is>
       </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -920,6 +926,9 @@
       <c r="F12" t="n">
         <v>8</v>
       </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -948,6 +957,9 @@
       <c r="F13" t="n">
         <v>6</v>
       </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -976,6 +988,9 @@
       <c r="F14" t="n">
         <v>6</v>
       </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1070,6 +1085,9 @@
       <c r="F17" t="n">
         <v>4</v>
       </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1098,6 +1116,9 @@
       <c r="F18" t="n">
         <v>1</v>
       </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1126,6 +1147,9 @@
       <c r="F19" t="n">
         <v>8</v>
       </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1154,6 +1178,9 @@
       <c r="F20" t="n">
         <v>2</v>
       </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1182,6 +1209,9 @@
       <c r="F21" t="n">
         <v>3</v>
       </c>
+      <c r="H21" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="F22" t="n">
         <v>2</v>
       </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1238,6 +1271,9 @@
       <c r="F23" t="n">
         <v>4</v>
       </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1266,6 +1302,9 @@
       <c r="F24" t="n">
         <v>3</v>
       </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1293,6 +1332,9 @@
       </c>
       <c r="F25" t="n">
         <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1677,6 +1719,9 @@
       <c r="F10" t="n">
         <v>3</v>
       </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1705,6 +1750,9 @@
       <c r="F11" t="n">
         <v>7</v>
       </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1733,6 +1781,9 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1761,6 +1812,9 @@
       <c r="F13" t="n">
         <v>2</v>
       </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1789,6 +1843,9 @@
       <c r="F14" t="n">
         <v>2</v>
       </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1817,6 +1874,9 @@
       <c r="F15" t="n">
         <v>5</v>
       </c>
+      <c r="H15" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1845,6 +1905,9 @@
       <c r="F16" t="n">
         <v>4</v>
       </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1873,6 +1936,9 @@
       <c r="F17" t="n">
         <v>6</v>
       </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1901,6 +1967,9 @@
       <c r="F18" t="n">
         <v>3</v>
       </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1929,6 +1998,9 @@
       <c r="F19" t="n">
         <v>8</v>
       </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1957,6 +2029,9 @@
       <c r="F20" t="n">
         <v>6</v>
       </c>
+      <c r="H20" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1985,6 +2060,9 @@
       <c r="F21" t="n">
         <v>7</v>
       </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2013,6 +2091,9 @@
       <c r="F22" t="n">
         <v>1</v>
       </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2041,6 +2122,9 @@
       <c r="F23" t="n">
         <v>8</v>
       </c>
+      <c r="H23" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2069,6 +2153,9 @@
       <c r="F24" t="n">
         <v>4</v>
       </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2096,6 +2183,9 @@
       </c>
       <c r="F25" t="n">
         <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2545,7 +2635,9 @@
         <v>2</v>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -2582,7 +2674,9 @@
         <v>1</v>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -2619,7 +2713,9 @@
         <v>3</v>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>8</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -2656,7 +2752,9 @@
         <v>5</v>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -2693,7 +2791,9 @@
         <v>3</v>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -2730,7 +2830,9 @@
         <v>2</v>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>7</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -2767,7 +2869,9 @@
         <v>7</v>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -2804,7 +2908,9 @@
         <v>6</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -2841,7 +2947,9 @@
         <v>4</v>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -2878,7 +2986,9 @@
         <v>1</v>
       </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -2915,7 +3025,9 @@
         <v>7</v>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -2952,7 +3064,9 @@
         <v>8</v>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -2989,7 +3103,9 @@
         <v>5</v>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -3026,7 +3142,9 @@
         <v>4</v>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -3063,7 +3181,9 @@
         <v>6</v>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>8</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -3100,7 +3220,9 @@
         <v>8</v>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>7</v>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -3675,6 +3797,9 @@
       <c r="E18" t="n">
         <v>13</v>
       </c>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3744,6 +3869,9 @@
       <c r="E21" t="n">
         <v>10</v>
       </c>
+      <c r="G21" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3767,6 +3895,9 @@
       <c r="E22" t="n">
         <v>4</v>
       </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3790,6 +3921,9 @@
       <c r="E23" t="n">
         <v>7</v>
       </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3813,6 +3947,9 @@
       <c r="E24" t="n">
         <v>15</v>
       </c>
+      <c r="G24" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3836,6 +3973,9 @@
       <c r="E25" t="n">
         <v>9</v>
       </c>
+      <c r="G25" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3859,6 +3999,9 @@
       <c r="E26" t="n">
         <v>7</v>
       </c>
+      <c r="G26" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3882,6 +4025,9 @@
       <c r="E27" t="n">
         <v>16</v>
       </c>
+      <c r="G27" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3905,6 +4051,9 @@
       <c r="E28" t="n">
         <v>11</v>
       </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3928,6 +4077,9 @@
       <c r="E29" t="n">
         <v>15</v>
       </c>
+      <c r="G29" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3951,6 +4103,9 @@
       <c r="E30" t="n">
         <v>5</v>
       </c>
+      <c r="G30" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3974,6 +4129,9 @@
       <c r="E31" t="n">
         <v>14</v>
       </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3997,6 +4155,9 @@
       <c r="E32" t="n">
         <v>12</v>
       </c>
+      <c r="G32" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4020,6 +4181,9 @@
       <c r="E33" t="n">
         <v>6</v>
       </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4043,6 +4207,9 @@
       <c r="E34" t="n">
         <v>12</v>
       </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4066,6 +4233,9 @@
       <c r="E35" t="n">
         <v>2</v>
       </c>
+      <c r="G35" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4089,6 +4259,9 @@
       <c r="E36" t="n">
         <v>1</v>
       </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4112,6 +4285,9 @@
       <c r="E37" t="n">
         <v>13</v>
       </c>
+      <c r="G37" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4135,6 +4311,9 @@
       <c r="E38" t="n">
         <v>8</v>
       </c>
+      <c r="G38" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4158,6 +4337,9 @@
       <c r="E39" t="n">
         <v>11</v>
       </c>
+      <c r="G39" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4181,6 +4363,9 @@
       <c r="E40" t="n">
         <v>4</v>
       </c>
+      <c r="G40" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4204,6 +4389,9 @@
       <c r="E41" t="n">
         <v>5</v>
       </c>
+      <c r="G41" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4227,6 +4415,9 @@
       <c r="E42" t="n">
         <v>14</v>
       </c>
+      <c r="G42" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4250,6 +4441,9 @@
       <c r="E43" t="n">
         <v>1</v>
       </c>
+      <c r="G43" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4273,6 +4467,9 @@
       <c r="E44" t="n">
         <v>6</v>
       </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4296,6 +4493,9 @@
       <c r="E45" t="n">
         <v>9</v>
       </c>
+      <c r="G45" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4319,6 +4519,9 @@
       <c r="E46" t="n">
         <v>3</v>
       </c>
+      <c r="G46" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4342,6 +4545,9 @@
       <c r="E47" t="n">
         <v>10</v>
       </c>
+      <c r="G47" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4365,6 +4571,9 @@
       <c r="E48" t="n">
         <v>8</v>
       </c>
+      <c r="G48" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4387,6 +4596,9 @@
       </c>
       <c r="E49" t="n">
         <v>2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4771,6 +4983,9 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4799,6 +5014,9 @@
       <c r="F11" t="n">
         <v>7</v>
       </c>
+      <c r="H11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4827,6 +5045,9 @@
       <c r="F12" t="n">
         <v>8</v>
       </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4855,6 +5076,9 @@
       <c r="F13" t="n">
         <v>3</v>
       </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4883,6 +5107,9 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4911,6 +5138,9 @@
       <c r="F15" t="n">
         <v>7</v>
       </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4939,6 +5169,9 @@
       <c r="F16" t="n">
         <v>3</v>
       </c>
+      <c r="H16" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4967,6 +5200,9 @@
       <c r="F17" t="n">
         <v>5</v>
       </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4995,6 +5231,9 @@
       <c r="F18" t="n">
         <v>6</v>
       </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5023,6 +5262,9 @@
       <c r="F19" t="n">
         <v>4</v>
       </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5051,6 +5293,9 @@
       <c r="F20" t="n">
         <v>2</v>
       </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5079,6 +5324,9 @@
       <c r="F21" t="n">
         <v>5</v>
       </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5107,6 +5355,9 @@
       <c r="F22" t="n">
         <v>4</v>
       </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5135,6 +5386,9 @@
       <c r="F23" t="n">
         <v>2</v>
       </c>
+      <c r="H23" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5163,6 +5417,9 @@
       <c r="F24" t="n">
         <v>6</v>
       </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5190,6 +5447,9 @@
       </c>
       <c r="F25" t="n">
         <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
